--- a/processed_quota_distinct_values.xlsx
+++ b/processed_quota_distinct_values.xlsx
@@ -469,12 +469,12 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -492,12 +492,12 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -515,12 +515,12 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -538,12 +538,12 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -561,12 +561,12 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -584,12 +584,12 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -607,12 +607,12 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -653,12 +653,12 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -676,12 +676,12 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1366,12 +1366,12 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1550,12 +1550,12 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1596,12 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1665,12 +1665,12 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1688,12 +1688,12 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1734,12 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1780,12 +1780,12 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1826,12 +1826,12 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1849,12 +1849,12 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1895,12 +1895,12 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1918,12 +1918,12 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1941,12 +1941,12 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -1987,12 +1987,12 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2010,12 +2010,12 @@
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2033,12 +2033,12 @@
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2056,12 +2056,12 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2079,12 +2079,12 @@
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2125,12 +2125,12 @@
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2148,12 +2148,12 @@
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2171,12 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2194,12 +2194,12 @@
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2240,12 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2263,12 +2263,12 @@
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2286,12 +2286,12 @@
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2309,12 +2309,12 @@
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2332,12 +2332,12 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2355,12 +2355,12 @@
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2378,12 +2378,12 @@
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2401,12 +2401,12 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2424,12 +2424,12 @@
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2470,12 +2470,12 @@
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2493,12 +2493,12 @@
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2516,12 +2516,12 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2539,12 +2539,12 @@
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2562,12 +2562,12 @@
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2585,12 +2585,12 @@
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2608,12 +2608,12 @@
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2631,12 +2631,12 @@
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2654,12 @@
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2700,12 +2700,12 @@
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2723,12 +2723,12 @@
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2746,12 +2746,12 @@
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2769,12 +2769,12 @@
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2815,12 +2815,12 @@
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2838,12 +2838,12 @@
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2861,12 +2861,12 @@
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2884,12 +2884,12 @@
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2907,12 +2907,12 @@
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2930,12 +2930,12 @@
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2953,12 +2953,12 @@
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2976,12 +2976,12 @@
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -2999,12 +2999,12 @@
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3045,12 +3045,12 @@
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3068,12 +3068,12 @@
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3091,12 +3091,12 @@
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3114,12 +3114,12 @@
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3137,12 +3137,12 @@
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3160,12 +3160,12 @@
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3183,12 +3183,12 @@
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3206,12 +3206,12 @@
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3252,12 +3252,12 @@
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3275,12 +3275,12 @@
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3298,12 +3298,12 @@
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3321,12 +3321,12 @@
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3390,12 +3390,12 @@
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3413,12 +3413,12 @@
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3436,12 +3436,12 @@
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3482,12 +3482,12 @@
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3505,12 +3505,12 @@
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3528,12 +3528,12 @@
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3551,12 +3551,12 @@
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3597,12 +3597,12 @@
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3620,12 +3620,12 @@
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3643,12 +3643,12 @@
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3666,12 +3666,12 @@
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3689,12 +3689,12 @@
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3735,12 +3735,12 @@
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3758,12 +3758,12 @@
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3781,12 @@
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3827,12 +3827,12 @@
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3850,12 +3850,12 @@
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3873,12 +3873,12 @@
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3896,12 +3896,12 @@
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3919,12 +3919,12 @@
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3942,12 +3942,12 @@
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3965,12 +3965,12 @@
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -3988,12 +3988,12 @@
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4057,12 +4057,12 @@
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4080,12 +4080,12 @@
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4103,12 +4103,12 @@
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4126,12 +4126,12 @@
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4172,12 +4172,12 @@
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4195,12 +4195,12 @@
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4218,12 +4218,12 @@
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4241,12 @@
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4264,12 +4264,12 @@
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4287,12 +4287,12 @@
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4310,12 +4310,12 @@
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4333,12 +4333,12 @@
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4356,12 +4356,12 @@
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4402,12 +4402,12 @@
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4425,12 +4425,12 @@
       <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4448,12 +4448,12 @@
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4471,12 +4471,12 @@
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4517,12 +4517,12 @@
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4540,12 +4540,12 @@
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4563,12 +4563,12 @@
       <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4586,12 @@
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4609,12 +4609,12 @@
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4632,12 +4632,12 @@
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4655,12 +4655,12 @@
       <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4678,12 +4678,12 @@
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4701,12 +4701,12 @@
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4724,12 @@
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4747,12 +4747,12 @@
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4770,12 +4770,12 @@
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4793,12 +4793,12 @@
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4816,12 +4816,12 @@
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4862,12 +4862,12 @@
       <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4885,12 +4885,12 @@
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4908,12 +4908,12 @@
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -4977,12 +4977,12 @@
       <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5000,12 +5000,12 @@
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5023,12 +5023,12 @@
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5046,12 +5046,12 @@
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5092,12 +5092,12 @@
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5115,12 +5115,12 @@
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5138,12 +5138,12 @@
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5207,12 +5207,12 @@
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5230,12 +5230,12 @@
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5253,12 +5253,12 @@
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5322,12 +5322,12 @@
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5345,12 +5345,12 @@
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5368,12 +5368,12 @@
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5414,12 +5414,12 @@
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5437,12 +5437,12 @@
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5460,12 +5460,12 @@
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5483,12 +5483,12 @@
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5552,12 +5552,12 @@
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5575,12 +5575,12 @@
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5598,12 +5598,12 @@
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5644,12 +5644,12 @@
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5667,12 +5667,12 @@
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5690,12 +5690,12 @@
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5713,12 +5713,12 @@
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5759,12 +5759,12 @@
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5782,12 +5782,12 @@
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5805,12 +5805,12 @@
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5828,12 +5828,12 @@
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5874,12 +5874,12 @@
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5897,12 +5897,12 @@
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5920,12 +5920,12 @@
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5943,12 +5943,12 @@
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -5989,12 +5989,12 @@
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6012,12 +6012,12 @@
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6035,12 +6035,12 @@
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6058,12 +6058,12 @@
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6081,12 +6081,12 @@
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6104,12 +6104,12 @@
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6127,12 +6127,12 @@
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6150,12 +6150,12 @@
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6173,12 @@
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6196,12 +6196,12 @@
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6219,12 +6219,12 @@
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6242,12 +6242,12 @@
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6265,12 +6265,12 @@
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6288,12 +6288,12 @@
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6311,12 +6311,12 @@
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6334,12 +6334,12 @@
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6357,12 +6357,12 @@
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6380,12 +6380,12 @@
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6403,12 +6403,12 @@
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6449,12 +6449,12 @@
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6472,12 +6472,12 @@
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6495,12 +6495,12 @@
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6518,12 +6518,12 @@
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6541,12 +6541,12 @@
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6564,12 +6564,12 @@
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6587,12 +6587,12 @@
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6610,12 +6610,12 @@
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6633,12 +6633,12 @@
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6656,12 +6656,12 @@
       <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6679,12 +6679,12 @@
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6702,12 +6702,12 @@
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6725,12 +6725,12 @@
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6748,12 +6748,12 @@
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6771,12 +6771,12 @@
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6794,12 +6794,12 @@
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6817,12 +6817,12 @@
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6840,12 +6840,12 @@
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6863,12 +6863,12 @@
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6886,12 +6886,12 @@
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6909,12 +6909,12 @@
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6932,12 +6932,12 @@
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6955,12 +6955,12 @@
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -6978,12 +6978,12 @@
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7001,12 +7001,12 @@
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7024,12 +7024,12 @@
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7047,12 +7047,12 @@
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7070,12 +7070,12 @@
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7093,12 +7093,12 @@
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7116,12 +7116,12 @@
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7139,12 +7139,12 @@
       <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7162,12 +7162,12 @@
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7185,12 +7185,12 @@
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7208,12 +7208,12 @@
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7231,12 +7231,12 @@
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7254,12 +7254,12 @@
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7277,12 +7277,12 @@
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7300,12 +7300,12 @@
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7323,12 +7323,12 @@
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7346,12 +7346,12 @@
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7369,12 +7369,12 @@
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7392,12 +7392,12 @@
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7415,12 +7415,12 @@
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7438,12 +7438,12 @@
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7461,12 +7461,12 @@
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7484,12 +7484,12 @@
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7507,12 +7507,12 @@
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7530,12 +7530,12 @@
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7576,12 +7576,12 @@
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7599,12 +7599,12 @@
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7622,12 +7622,12 @@
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7645,12 +7645,12 @@
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7668,12 +7668,12 @@
       <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7691,12 +7691,12 @@
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7714,12 +7714,12 @@
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7737,12 +7737,12 @@
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7760,12 +7760,12 @@
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7783,12 +7783,12 @@
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7829,12 +7829,12 @@
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7852,12 +7852,12 @@
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7875,12 +7875,12 @@
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7898,12 @@
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7944,12 +7944,12 @@
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7967,12 +7967,12 @@
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -7990,12 +7990,12 @@
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8082,12 +8082,12 @@
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8105,12 +8105,12 @@
       <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8151,12 +8151,12 @@
       <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8197,12 +8197,12 @@
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8220,12 +8220,12 @@
       <c r="C339" t="inlineStr"/>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8289,12 +8289,12 @@
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8312,12 +8312,12 @@
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8335,12 +8335,12 @@
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8358,12 +8358,12 @@
       <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8381,12 +8381,12 @@
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8404,12 +8404,12 @@
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8427,12 +8427,12 @@
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8450,12 +8450,12 @@
       <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8473,12 +8473,12 @@
       <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8542,12 +8542,12 @@
       <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8565,12 +8565,12 @@
       <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8588,12 +8588,12 @@
       <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8611,12 +8611,12 @@
       <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8634,12 +8634,12 @@
       <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8657,12 +8657,12 @@
       <c r="C358" t="inlineStr"/>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8680,12 +8680,12 @@
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8703,12 +8703,12 @@
       <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8726,12 +8726,12 @@
       <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8772,12 +8772,12 @@
       <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8795,12 +8795,12 @@
       <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8818,12 +8818,12 @@
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8841,12 +8841,12 @@
       <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8887,12 +8887,12 @@
       <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8910,12 +8910,12 @@
       <c r="C369" t="inlineStr"/>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8956,12 +8956,12 @@
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -8979,12 +8979,12 @@
       <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9002,12 +9002,12 @@
       <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9025,12 +9025,12 @@
       <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9048,12 +9048,12 @@
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9071,12 +9071,12 @@
       <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9117,12 +9117,12 @@
       <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9140,12 +9140,12 @@
       <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       <c r="C380" t="inlineStr"/>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9186,12 +9186,12 @@
       <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9209,12 +9209,12 @@
       <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9232,12 +9232,12 @@
       <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9255,12 +9255,12 @@
       <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9278,12 +9278,12 @@
       <c r="C385" t="inlineStr"/>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9301,12 +9301,12 @@
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       <c r="C387" t="inlineStr"/>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9347,12 +9347,12 @@
       <c r="C388" t="inlineStr"/>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9370,12 +9370,12 @@
       <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9393,12 +9393,12 @@
       <c r="C390" t="inlineStr"/>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9416,12 +9416,12 @@
       <c r="C391" t="inlineStr"/>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9439,12 +9439,12 @@
       <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9462,12 +9462,12 @@
       <c r="C393" t="inlineStr"/>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9485,12 +9485,12 @@
       <c r="C394" t="inlineStr"/>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9508,12 +9508,12 @@
       <c r="C395" t="inlineStr"/>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9531,12 +9531,12 @@
       <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9554,12 +9554,12 @@
       <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9577,12 +9577,12 @@
       <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9600,12 +9600,12 @@
       <c r="C399" t="inlineStr"/>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9623,12 +9623,12 @@
       <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9646,12 +9646,12 @@
       <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9669,12 +9669,12 @@
       <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9692,12 +9692,12 @@
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9715,12 +9715,12 @@
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9738,12 +9738,12 @@
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9761,12 +9761,12 @@
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9784,12 +9784,12 @@
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9807,12 +9807,12 @@
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9830,12 +9830,12 @@
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9853,12 +9853,12 @@
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9876,12 +9876,12 @@
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9899,12 +9899,12 @@
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9922,12 +9922,12 @@
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9968,12 +9968,12 @@
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -9991,12 +9991,12 @@
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10014,12 +10014,12 @@
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10037,12 +10037,12 @@
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10060,12 +10060,12 @@
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10083,12 +10083,12 @@
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10106,12 +10106,12 @@
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10129,12 +10129,12 @@
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10152,12 +10152,12 @@
       <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10198,12 +10198,12 @@
       <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10221,12 +10221,12 @@
       <c r="C426" t="inlineStr"/>
       <c r="D426" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10244,12 +10244,12 @@
       <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10267,12 +10267,12 @@
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10290,12 +10290,12 @@
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10313,12 +10313,12 @@
       <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10336,12 +10336,12 @@
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10359,12 +10359,12 @@
       <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10382,12 +10382,12 @@
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       <c r="C434" t="inlineStr"/>
       <c r="D434" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10428,12 +10428,12 @@
       <c r="C435" t="inlineStr"/>
       <c r="D435" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10451,12 +10451,12 @@
       <c r="C436" t="inlineStr"/>
       <c r="D436" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10474,12 +10474,12 @@
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10497,12 +10497,12 @@
       <c r="C438" t="inlineStr"/>
       <c r="D438" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10520,12 +10520,12 @@
       <c r="C439" t="inlineStr"/>
       <c r="D439" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10543,12 +10543,12 @@
       <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10566,12 +10566,12 @@
       <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10589,12 +10589,12 @@
       <c r="C442" t="inlineStr"/>
       <c r="D442" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10612,12 +10612,12 @@
       <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10635,12 +10635,12 @@
       <c r="C444" t="inlineStr"/>
       <c r="D444" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10658,12 +10658,12 @@
       <c r="C445" t="inlineStr"/>
       <c r="D445" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10681,12 +10681,12 @@
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10704,12 +10704,12 @@
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10727,12 +10727,12 @@
       <c r="C448" t="inlineStr"/>
       <c r="D448" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10750,12 +10750,12 @@
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10773,12 +10773,12 @@
       <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10796,12 +10796,12 @@
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10819,12 +10819,12 @@
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10842,12 +10842,12 @@
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10865,12 +10865,12 @@
       <c r="C454" t="inlineStr"/>
       <c r="D454" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10888,12 +10888,12 @@
       <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10911,12 +10911,12 @@
       <c r="C456" t="inlineStr"/>
       <c r="D456" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10934,12 +10934,12 @@
       <c r="C457" t="inlineStr"/>
       <c r="D457" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10957,12 +10957,12 @@
       <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -10980,12 +10980,12 @@
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11003,12 +11003,12 @@
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11026,12 +11026,12 @@
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11049,12 +11049,12 @@
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11072,12 +11072,12 @@
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11095,12 +11095,12 @@
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11118,12 +11118,12 @@
       <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11141,12 +11141,12 @@
       <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11164,12 +11164,12 @@
       <c r="C467" t="inlineStr"/>
       <c r="D467" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11187,12 +11187,12 @@
       <c r="C468" t="inlineStr"/>
       <c r="D468" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11210,12 +11210,12 @@
       <c r="C469" t="inlineStr"/>
       <c r="D469" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11233,12 +11233,12 @@
       <c r="C470" t="inlineStr"/>
       <c r="D470" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11256,12 +11256,12 @@
       <c r="C471" t="inlineStr"/>
       <c r="D471" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11279,12 +11279,12 @@
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11302,12 +11302,12 @@
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11325,12 +11325,12 @@
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11371,12 +11371,12 @@
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11394,12 +11394,12 @@
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11417,12 +11417,12 @@
       <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11440,12 +11440,12 @@
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11486,12 +11486,12 @@
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11509,12 +11509,12 @@
       <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11532,12 +11532,12 @@
       <c r="C483" t="inlineStr"/>
       <c r="D483" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
@@ -11555,12 +11555,12 @@
       <c r="C484" t="inlineStr"/>
       <c r="D484" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>2026-01-14 21:50:00</t>
+          <t>2026-02-03 11:14:09</t>
         </is>
       </c>
     </row>
